--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9176,0.0738,0.0116,0.0010</t>
-  </si>
-  <si>
-    <t>0.9856,0.0065,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.9225,0.0689,0.0058,0.0018</t>
-  </si>
-  <si>
-    <t>0.9499,0.0399,0.0035,0.0016</t>
-  </si>
-  <si>
-    <t>0.8216,0.2709,0.0090,0.0012</t>
-  </si>
-  <si>
-    <t>0.9211,0.0605,0.0026,0.0015</t>
-  </si>
-  <si>
-    <t>0.9702,0.0220,0.0025,0.0013</t>
-  </si>
-  <si>
-    <t>0.9681,0.0190,0.0021,0.0018</t>
-  </si>
-  <si>
-    <t>0.8545,0.2302,0.0033,0.0007</t>
-  </si>
-  <si>
-    <t>0.8205,0.1990,0.0073,0.0017</t>
-  </si>
-  <si>
-    <t>0.9668,0.0247,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.8828,0.1384,0.0046,0.0011</t>
-  </si>
-  <si>
-    <t>0.9850,0.0046,0.0083,0.0001</t>
-  </si>
-  <si>
-    <t>0.9315,0.0286,0.0302,0.0003</t>
-  </si>
-  <si>
-    <t>0.9870,0.0039,0.0061,0.0001</t>
-  </si>
-  <si>
-    <t>0.9919,0.0012,0.0067,0.0001</t>
-  </si>
-  <si>
-    <t>0.9563,0.0292,0.0107,0.0006</t>
-  </si>
-  <si>
-    <t>0.7084,0.4362,0.0095,0.0004</t>
-  </si>
-  <si>
-    <t>0.9161,0.1172,0.0067,0.0002</t>
-  </si>
-  <si>
-    <t>0.8883,0.1316,0.0078,0.0005</t>
-  </si>
-  <si>
-    <t>0.4868,0.7327,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.3416,0.8080,0.0064,0.0003</t>
-  </si>
-  <si>
-    <t>0.8479,0.0471,0.1081,0.0022</t>
-  </si>
-  <si>
-    <t>0.9939,0.0007,0.0058,0.0001</t>
-  </si>
-  <si>
-    <t>0.9430,0.0035,0.0910,0.0003</t>
-  </si>
-  <si>
-    <t>0.9853,0.0017,0.0169,0.0001</t>
-  </si>
-  <si>
-    <t>0.9773,0.0046,0.0206,0.0005</t>
-  </si>
-  <si>
-    <t>0.9540,0.0062,0.0624,0.0004</t>
-  </si>
-  <si>
-    <t>0.8792,0.0158,0.0892,0.0005</t>
-  </si>
-  <si>
-    <t>0.9764,0.0494,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9847,0.0147,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0255,0.2973,0.9580,0.0013</t>
-  </si>
-  <si>
-    <t>0.6089,0.5173,0.0110,0.0002</t>
-  </si>
-  <si>
-    <t>0.9338,0.0792,0.0065,0.0005</t>
-  </si>
-  <si>
-    <t>0.7671,0.3167,0.0137,0.0010</t>
-  </si>
-  <si>
-    <t>0.7819,0.3119,0.0062,0.0012</t>
-  </si>
-  <si>
-    <t>0.9349,0.0945,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.9772,0.0037,0.0142,0.0001</t>
-  </si>
-  <si>
-    <t>0.8647,0.0032,0.2162,0.0011</t>
-  </si>
-  <si>
-    <t>0.9786,0.0009,0.0476,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0003,0.0047,0.0000</t>
-  </si>
-  <si>
-    <t>0.8996,0.0082,0.1540,0.0003</t>
-  </si>
-  <si>
-    <t>0.6473,0.1086,0.0632,0.0002</t>
-  </si>
-  <si>
-    <t>0.9948,0.0003,0.0057,0.0000</t>
-  </si>
-  <si>
-    <t>0.9125,0.0941,0.0056,0.0014</t>
-  </si>
-  <si>
-    <t>0.8673,0.2177,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.9664,0.0415,0.0030,0.0000</t>
-  </si>
-  <si>
-    <t>0.6367,0.5049,0.0033,0.0000</t>
-  </si>
-  <si>
-    <t>0.3876,0.0049,0.7958,0.0012</t>
-  </si>
-  <si>
-    <t>0.2180,0.0060,0.8874,0.0003</t>
-  </si>
-  <si>
-    <t>0.7936,0.0121,0.2995,0.0032</t>
-  </si>
-  <si>
-    <t>0.7627,0.0357,0.2496,0.0012</t>
-  </si>
-  <si>
-    <t>0.0147,0.0310,0.9875,0.0003</t>
-  </si>
-  <si>
-    <t>0.8976,0.0049,0.1952,0.0005</t>
-  </si>
-  <si>
-    <t>0.9377,0.0904,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.9820,0.0128,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9690,0.0197,0.0012,0.0015</t>
-  </si>
-  <si>
-    <t>0.0587,0.5848,0.8924,0.0067</t>
-  </si>
-  <si>
-    <t>0.8392,0.2034,0.0050,0.0015</t>
-  </si>
-  <si>
-    <t>0.9289,0.0964,0.0028,0.0008</t>
-  </si>
-  <si>
-    <t>0.9011,0.0712,0.0045,0.0031</t>
-  </si>
-  <si>
-    <t>0.5726,0.0529,0.4528,0.0010</t>
-  </si>
-  <si>
-    <t>0.2657,0.0097,0.8644,0.0006</t>
-  </si>
-  <si>
-    <t>0.7115,0.0214,0.2359,0.0013</t>
-  </si>
-  <si>
-    <t>0.2377,0.7744,0.0399,0.0002</t>
-  </si>
-  <si>
-    <t>0.4952,0.0040,0.7286,0.0004</t>
-  </si>
-  <si>
-    <t>0.9822,0.0155,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.6334,0.3904,0.0082,0.0001</t>
-  </si>
-  <si>
-    <t>0.9395,0.0662,0.0065,0.0004</t>
-  </si>
-  <si>
-    <t>0.9327,0.0951,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.0804,0.5792,0.8431,0.0048</t>
-  </si>
-  <si>
-    <t>0.7194,0.0711,0.0798,0.0003</t>
-  </si>
-  <si>
-    <t>0.9677,0.0022,0.0531,0.0002</t>
-  </si>
-  <si>
-    <t>0.5075,0.4051,0.0254,0.0001</t>
-  </si>
-  <si>
-    <t>0.8377,0.0537,0.0639,0.0003</t>
-  </si>
-  <si>
-    <t>0.9521,0.0230,0.0088,0.0022</t>
-  </si>
-  <si>
-    <t>0.8612,0.0387,0.0021,0.0277</t>
-  </si>
-  <si>
-    <t>0.9737,0.0162,0.0025,0.0014</t>
-  </si>
-  <si>
-    <t>0.9758,0.0083,0.0027,0.0031</t>
-  </si>
-  <si>
-    <t>0.9606,0.0128,0.0084,0.0039</t>
-  </si>
-  <si>
-    <t>0.9633,0.0146,0.0052,0.0032</t>
-  </si>
-  <si>
-    <t>0.8529,0.0518,0.0531,0.0002</t>
-  </si>
-  <si>
-    <t>0.3998,0.0130,0.7717,0.0006</t>
-  </si>
-  <si>
-    <t>0.4648,0.0062,0.7216,0.0002</t>
-  </si>
-  <si>
-    <t>0.8988,0.0161,0.0938,0.0002</t>
-  </si>
-  <si>
-    <t>0.1192,0.2051,0.7858,0.0013</t>
-  </si>
-  <si>
-    <t>0.8100,0.0418,0.1144,0.0006</t>
-  </si>
-  <si>
-    <t>0.9370,0.0691,0.0018,0.0008</t>
-  </si>
-  <si>
-    <t>0.4550,0.6636,0.0228,0.0025</t>
-  </si>
-  <si>
-    <t>0.9213,0.0826,0.0042,0.0010</t>
-  </si>
-  <si>
-    <t>0.9581,0.0284,0.0010,0.0012</t>
-  </si>
-  <si>
-    <t>0.9228,0.0818,0.0048,0.0017</t>
-  </si>
-  <si>
-    <t>0.9174,0.0894,0.0032,0.0009</t>
-  </si>
-  <si>
-    <t>0.7841,0.3307,0.0081,0.0015</t>
-  </si>
-  <si>
-    <t>0.8070,0.2429,0.0096,0.0016</t>
-  </si>
-  <si>
-    <t>0.6201,0.5368,0.0179,0.0016</t>
-  </si>
-  <si>
-    <t>0.9715,0.0175,0.0018,0.0018</t>
-  </si>
-  <si>
-    <t>0.9713,0.0149,0.0008,0.0014</t>
-  </si>
-  <si>
-    <t>0.9735,0.0232,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9729,0.0250,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.8949,0.1871,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9539,0.0279,0.0020,0.0022</t>
-  </si>
-  <si>
-    <t>0.8293,0.1811,0.0149,0.0051</t>
-  </si>
-  <si>
-    <t>0.1757,0.0665,0.8404,0.0009</t>
-  </si>
-  <si>
-    <t>0.9695,0.0028,0.0347,0.0001</t>
-  </si>
-  <si>
-    <t>0.9838,0.0029,0.0131,0.0002</t>
-  </si>
-  <si>
-    <t>0.9811,0.0036,0.0195,0.0002</t>
-  </si>
-  <si>
-    <t>0.2988,0.8448,0.0087,0.0004</t>
-  </si>
-  <si>
-    <t>0.8722,0.1970,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.9718,0.0380,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9542,0.0706,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.5740,0.6157,0.0060,0.0004</t>
-  </si>
-  <si>
-    <t>0.1057,0.9421,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.8170,0.3448,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.9879,0.0051,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.9448,0.0085,0.0651,0.0013</t>
-  </si>
-  <si>
-    <t>0.9292,0.0642,0.0107,0.0006</t>
-  </si>
-  <si>
-    <t>0.9577,0.0293,0.0107,0.0003</t>
-  </si>
-  <si>
-    <t>0.7394,0.2485,0.0470,0.0039</t>
-  </si>
-  <si>
-    <t>0.9868,0.0115,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.9536,0.0422,0.0046,0.0001</t>
-  </si>
-  <si>
-    <t>0.9468,0.0272,0.0101,0.0004</t>
-  </si>
-  <si>
-    <t>0.2414,0.1201,0.3127,0.0002</t>
-  </si>
-  <si>
-    <t>0.9295,0.1179,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.9226,0.0895,0.0063,0.0006</t>
-  </si>
-  <si>
-    <t>0.6969,0.4101,0.0152,0.0011</t>
-  </si>
-  <si>
-    <t>0.9644,0.0493,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9700,0.0148,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.8818,0.1301,0.0061,0.0019</t>
-  </si>
-  <si>
-    <t>0.9646,0.0306,0.0028,0.0007</t>
-  </si>
-  <si>
-    <t>0.9677,0.0192,0.0011,0.0016</t>
-  </si>
-  <si>
-    <t>0.9691,0.0297,0.0031,0.0006</t>
-  </si>
-  <si>
-    <t>0.8812,0.1133,0.0053,0.0024</t>
-  </si>
-  <si>
-    <t>0.9488,0.0586,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.9456,0.0045,0.0954,0.0003</t>
-  </si>
-  <si>
-    <t>0.9208,0.0035,0.1756,0.0003</t>
-  </si>
-  <si>
-    <t>0.5387,0.0130,0.5799,0.0026</t>
-  </si>
-  <si>
-    <t>0.9832,0.0007,0.0357,0.0001</t>
-  </si>
-  <si>
-    <t>0.9858,0.0078,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.9453,0.0484,0.0053,0.0005</t>
-  </si>
-  <si>
-    <t>0.9216,0.0303,0.0378,0.0014</t>
-  </si>
-  <si>
-    <t>0.9284,0.0641,0.0113,0.0005</t>
-  </si>
-  <si>
-    <t>0.9719,0.0117,0.0014,0.0012</t>
-  </si>
-  <si>
-    <t>0.7896,0.0193,0.0479,0.1202</t>
-  </si>
-  <si>
-    <t>0.9291,0.0227,0.0306,0.0045</t>
-  </si>
-  <si>
-    <t>0.9432,0.0150,0.0068,0.0079</t>
-  </si>
-  <si>
-    <t>0.6270,0.1385,0.1491,0.0007</t>
-  </si>
-  <si>
-    <t>0.9038,0.0877,0.0079,0.0026</t>
-  </si>
-  <si>
-    <t>0.8543,0.2030,0.0082,0.0011</t>
-  </si>
-  <si>
-    <t>0.9329,0.0713,0.0017,0.0009</t>
-  </si>
-  <si>
-    <t>0.9590,0.0394,0.0025,0.0004</t>
-  </si>
-  <si>
-    <t>0.8218,0.2388,0.0054,0.0015</t>
-  </si>
-  <si>
-    <t>0.9689,0.0182,0.0033,0.0010</t>
-  </si>
-  <si>
-    <t>0.8223,0.1983,0.0133,0.0026</t>
-  </si>
-  <si>
-    <t>0.5916,0.2663,0.3033,0.0153</t>
-  </si>
-  <si>
-    <t>0.9679,0.0146,0.0028,0.0017</t>
-  </si>
-  <si>
-    <t>0.8436,0.1477,0.0190,0.0040</t>
-  </si>
-  <si>
-    <t>0.9740,0.0205,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.9009,0.1085,0.0084,0.0008</t>
-  </si>
-  <si>
-    <t>0.9777,0.0161,0.0036,0.0002</t>
-  </si>
-  <si>
-    <t>0.9110,0.0943,0.0114,0.0009</t>
-  </si>
-  <si>
-    <t>0.9384,0.0696,0.0062,0.0002</t>
-  </si>
-  <si>
-    <t>0.9167,0.1233,0.0036,0.0006</t>
-  </si>
-  <si>
-    <t>0.8877,0.1331,0.0074,0.0017</t>
-  </si>
-  <si>
-    <t>0.8488,0.2002,0.0035,0.0011</t>
-  </si>
-  <si>
-    <t>0.9877,0.0098,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9360,0.0455,0.0031,0.0021</t>
-  </si>
-  <si>
-    <t>0.9571,0.0307,0.0016,0.0015</t>
-  </si>
-  <si>
-    <t>0.8183,0.2120,0.0060,0.0020</t>
-  </si>
-  <si>
-    <t>0.9527,0.0329,0.0021,0.0016</t>
-  </si>
-  <si>
-    <t>0.9389,0.0496,0.0040,0.0018</t>
-  </si>
-  <si>
-    <t>0.8010,0.2869,0.0071,0.0006</t>
-  </si>
-  <si>
-    <t>0.9921,0.0056,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.7266,0.3602,0.0087,0.0012</t>
-  </si>
-  <si>
-    <t>0.9600,0.0318,0.0030,0.0008</t>
-  </si>
-  <si>
-    <t>0.9410,0.0722,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.9434,0.0721,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.8926,0.2084,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9576,0.0622,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.0072,0.1373,0.9891,0.0003</t>
-  </si>
-  <si>
-    <t>0.9760,0.0140,0.0021,0.0010</t>
-  </si>
-  <si>
-    <t>0.5259,0.0019,0.7095,0.0003</t>
-  </si>
-  <si>
-    <t>0.9665,0.0026,0.0475,0.0002</t>
-  </si>
-  <si>
-    <t>0.9885,0.0010,0.0134,0.0001</t>
-  </si>
-  <si>
-    <t>0.3109,0.0109,0.8663,0.0001</t>
-  </si>
-  <si>
-    <t>0.9601,0.0031,0.0563,0.0002</t>
-  </si>
-  <si>
-    <t>0.6756,0.0024,0.5840,0.0001</t>
-  </si>
-  <si>
-    <t>0.7666,0.0317,0.2736,0.0012</t>
-  </si>
-  <si>
-    <t>0.9558,0.0204,0.0150,0.0003</t>
-  </si>
-  <si>
-    <t>0.9897,0.0039,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.8769,0.0650,0.0499,0.0006</t>
-  </si>
-  <si>
-    <t>0.9017,0.0482,0.0341,0.0008</t>
-  </si>
-  <si>
-    <t>0.8931,0.0594,0.0378,0.0005</t>
-  </si>
-  <si>
-    <t>0.9810,0.0075,0.0084,0.0002</t>
-  </si>
-  <si>
-    <t>0.8317,0.1857,0.0113,0.0005</t>
-  </si>
-  <si>
-    <t>0.8894,0.0658,0.0287,0.0005</t>
-  </si>
-  <si>
-    <t>0.6869,0.5055,0.0050,0.0003</t>
-  </si>
-  <si>
-    <t>0.8401,0.2965,0.0034,0.0006</t>
-  </si>
-  <si>
-    <t>0.4222,0.7593,0.0055,0.0007</t>
-  </si>
-  <si>
-    <t>0.9760,0.0275,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9380,0.0847,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9912,0.0027,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.9549,0.0146,0.0303,0.0010</t>
-  </si>
-  <si>
-    <t>0.9837,0.0038,0.0090,0.0003</t>
-  </si>
-  <si>
-    <t>0.9863,0.0045,0.0076,0.0001</t>
-  </si>
-  <si>
-    <t>0.9179,0.0327,0.0395,0.0014</t>
-  </si>
-  <si>
-    <t>0.0771,0.5764,0.3444,0.0005</t>
-  </si>
-  <si>
-    <t>0.9229,0.0089,0.1037,0.0012</t>
-  </si>
-  <si>
-    <t>0.9718,0.0065,0.0213,0.0002</t>
-  </si>
-  <si>
-    <t>0.8106,0.0029,0.4062,0.0006</t>
-  </si>
-  <si>
-    <t>0.9509,0.0012,0.1051,0.0001</t>
-  </si>
-  <si>
-    <t>0.9874,0.0118,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.7861,0.3168,0.0066,0.0012</t>
-  </si>
-  <si>
-    <t>0.7018,0.4128,0.0167,0.0020</t>
-  </si>
-  <si>
-    <t>0.9135,0.0759,0.0018,0.0017</t>
-  </si>
-  <si>
-    <t>0.8470,0.1825,0.0082,0.0014</t>
-  </si>
-  <si>
-    <t>0.9646,0.0510,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.7755,0.2413,0.0111,0.0025</t>
-  </si>
-  <si>
-    <t>0.8989,0.1336,0.0082,0.0010</t>
-  </si>
-  <si>
-    <t>0.7619,0.1089,0.2099,0.0044</t>
-  </si>
-  <si>
-    <t>0.7548,0.1432,0.0650,0.0008</t>
-  </si>
-  <si>
-    <t>0.6749,0.4155,0.0218,0.0014</t>
-  </si>
-  <si>
-    <t>0.0184,0.0817,0.9680,0.0002</t>
-  </si>
-  <si>
-    <t>0.1510,0.0375,0.8363,0.0015</t>
-  </si>
-  <si>
-    <t>0.9822,0.0023,0.0205,0.0003</t>
-  </si>
-  <si>
-    <t>0.4578,0.0035,0.8075,0.0002</t>
-  </si>
-  <si>
-    <t>0.8590,0.0049,0.2555,0.0005</t>
-  </si>
-  <si>
-    <t>0.0620,0.0193,0.9553,0.0010</t>
-  </si>
-  <si>
-    <t>0.8871,0.0036,0.2557,0.0005</t>
-  </si>
-  <si>
-    <t>0.9536,0.0189,0.0160,0.0008</t>
-  </si>
-  <si>
-    <t>0.9913,0.0014,0.0045,0.0002</t>
-  </si>
-  <si>
-    <t>0.9526,0.0134,0.0301,0.0005</t>
-  </si>
-  <si>
-    <t>0.9631,0.0168,0.0147,0.0004</t>
-  </si>
-  <si>
-    <t>0.6727,0.4878,0.0070,0.0006</t>
-  </si>
-  <si>
-    <t>0.8899,0.1661,0.0049,0.0005</t>
-  </si>
-  <si>
-    <t>0.8601,0.1300,0.0012,0.0008</t>
-  </si>
-  <si>
-    <t>0.9476,0.0545,0.0027,0.0015</t>
-  </si>
-  <si>
-    <t>0.8775,0.0992,0.0030,0.0020</t>
-  </si>
-  <si>
-    <t>0.8977,0.1413,0.0051,0.0013</t>
-  </si>
-  <si>
-    <t>0.9784,0.0213,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9504,0.0779,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9582,0.0114,0.0242,0.0002</t>
-  </si>
-  <si>
-    <t>0.5846,0.0184,0.4970,0.0003</t>
-  </si>
-  <si>
-    <t>0.3844,0.0854,0.3199,0.0004</t>
-  </si>
-  <si>
-    <t>0.9660,0.0076,0.0304,0.0006</t>
-  </si>
-  <si>
-    <t>0.9521,0.0015,0.0874,0.0002</t>
-  </si>
-  <si>
-    <t>0.9516,0.0101,0.0493,0.0008</t>
-  </si>
-  <si>
-    <t>0.9829,0.0016,0.0240,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0001,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.9132,0.0460,0.0127,0.0059</t>
-  </si>
-  <si>
-    <t>0.9605,0.0180,0.0178,0.0009</t>
-  </si>
-  <si>
-    <t>0.9735,0.0115,0.0029,0.0012</t>
-  </si>
-  <si>
-    <t>0.9743,0.0077,0.0055,0.0026</t>
-  </si>
-  <si>
-    <t>0.7564,0.0477,0.0339,0.1905</t>
-  </si>
-  <si>
-    <t>0.9636,0.0178,0.0116,0.0006</t>
+    <t>0.6322,0.0125,0.0010,0.3503</t>
+  </si>
+  <si>
+    <t>0.0102,0.0002,0.0001,0.9976</t>
+  </si>
+  <si>
+    <t>0.9726,0.0016,0.0002,0.0129</t>
+  </si>
+  <si>
+    <t>0.0771,0.0013,0.0008,0.9759</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0013,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0012,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9951,0.0030,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9985,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.7981,0.0417,0.1378,0.0055</t>
+  </si>
+  <si>
+    <t>0.5844,0.0130,0.5644,0.0009</t>
+  </si>
+  <si>
+    <t>0.1599,0.0004,0.9597,0.0000</t>
+  </si>
+  <si>
+    <t>0.0207,0.0148,0.9621,0.0068</t>
+  </si>
+  <si>
+    <t>0.9773,0.0012,0.0260,0.0007</t>
+  </si>
+  <si>
+    <t>0.0058,0.9924,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.0146,0.9825,0.0043,0.0037</t>
+  </si>
+  <si>
+    <t>0.0405,0.9558,0.0121,0.0034</t>
+  </si>
+  <si>
+    <t>0.0052,0.9920,0.0031,0.0008</t>
+  </si>
+  <si>
+    <t>0.0024,0.9930,0.0061,0.0020</t>
+  </si>
+  <si>
+    <t>0.7425,0.0061,0.3594,0.0085</t>
+  </si>
+  <si>
+    <t>0.5843,0.0026,0.5156,0.0054</t>
+  </si>
+  <si>
+    <t>0.0034,0.0009,0.9929,0.0021</t>
+  </si>
+  <si>
+    <t>0.1385,0.0632,0.7790,0.0090</t>
+  </si>
+  <si>
+    <t>0.0988,0.0056,0.9428,0.0014</t>
+  </si>
+  <si>
+    <t>0.0393,0.0033,0.9692,0.0015</t>
+  </si>
+  <si>
+    <t>0.0034,0.0014,0.9970,0.0002</t>
+  </si>
+  <si>
+    <t>0.0925,0.9087,0.0217,0.0199</t>
+  </si>
+  <si>
+    <t>0.6643,0.1777,0.2987,0.0193</t>
+  </si>
+  <si>
+    <t>0.0035,0.0037,0.9942,0.0019</t>
+  </si>
+  <si>
+    <t>0.0142,0.9610,0.0430,0.0002</t>
+  </si>
+  <si>
+    <t>0.8214,0.1300,0.0438,0.0535</t>
+  </si>
+  <si>
+    <t>0.5917,0.0302,0.4886,0.0021</t>
+  </si>
+  <si>
+    <t>0.7955,0.3020,0.0107,0.0003</t>
+  </si>
+  <si>
+    <t>0.0211,0.9499,0.2460,0.0017</t>
+  </si>
+  <si>
+    <t>0.0172,0.0208,0.9479,0.0099</t>
+  </si>
+  <si>
+    <t>0.6686,0.0013,0.4984,0.0027</t>
+  </si>
+  <si>
+    <t>0.0802,0.0508,0.9171,0.0079</t>
+  </si>
+  <si>
+    <t>0.0204,0.0007,0.9662,0.0077</t>
+  </si>
+  <si>
+    <t>0.0051,0.1769,0.9864,0.0012</t>
+  </si>
+  <si>
+    <t>0.0052,0.7157,0.3409,0.0009</t>
+  </si>
+  <si>
+    <t>0.0099,0.0047,0.9845,0.0038</t>
+  </si>
+  <si>
+    <t>0.1588,0.2067,0.0208,0.8271</t>
+  </si>
+  <si>
+    <t>0.0063,0.9807,0.0067,0.0060</t>
+  </si>
+  <si>
+    <t>0.0207,0.9200,0.1540,0.0071</t>
+  </si>
+  <si>
+    <t>0.0070,0.9797,0.0231,0.0082</t>
+  </si>
+  <si>
+    <t>0.0039,0.0116,0.9859,0.0050</t>
+  </si>
+  <si>
+    <t>0.0014,0.0401,0.9948,0.0016</t>
+  </si>
+  <si>
+    <t>0.0123,0.0029,0.9788,0.0089</t>
+  </si>
+  <si>
+    <t>0.1034,0.0017,0.9682,0.0002</t>
+  </si>
+  <si>
+    <t>0.0092,0.0025,0.9917,0.0008</t>
+  </si>
+  <si>
+    <t>0.0047,0.0090,0.9912,0.0007</t>
+  </si>
+  <si>
+    <t>0.9897,0.0124,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9902,0.0025,0.0042,0.0012</t>
+  </si>
+  <si>
+    <t>0.9903,0.0007,0.0016,0.0064</t>
+  </si>
+  <si>
+    <t>0.0118,0.0336,0.9862,0.0059</t>
+  </si>
+  <si>
+    <t>0.9969,0.0011,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9897,0.0060,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.0012,0.4620,0.9961,0.0006</t>
+  </si>
+  <si>
+    <t>0.0051,0.0038,0.9949,0.0010</t>
+  </si>
+  <si>
+    <t>0.0036,0.0206,0.9899,0.0035</t>
+  </si>
+  <si>
+    <t>0.0016,0.9678,0.9199,0.0011</t>
+  </si>
+  <si>
+    <t>0.0057,0.0042,0.9935,0.0010</t>
+  </si>
+  <si>
+    <t>0.0384,0.9653,0.0076,0.0004</t>
+  </si>
+  <si>
+    <t>0.0039,0.9942,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9262,0.0049,0.1641,0.0004</t>
+  </si>
+  <si>
+    <t>0.4480,0.0841,0.6281,0.0073</t>
+  </si>
+  <si>
+    <t>0.0019,0.0269,0.9944,0.0058</t>
+  </si>
+  <si>
+    <t>0.0014,0.8995,0.9819,0.0004</t>
+  </si>
+  <si>
+    <t>0.0045,0.7222,0.9767,0.0010</t>
+  </si>
+  <si>
+    <t>0.0047,0.9859,0.1809,0.0009</t>
+  </si>
+  <si>
+    <t>0.0039,0.9530,0.5652,0.0003</t>
+  </si>
+  <si>
+    <t>0.0069,0.0022,0.0015,0.9954</t>
+  </si>
+  <si>
+    <t>0.0008,0.0021,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0046,0.0118,0.0004,0.9968</t>
+  </si>
+  <si>
+    <t>0.0048,0.0023,0.0010,0.9972</t>
+  </si>
+  <si>
+    <t>0.0071,0.0006,0.0011,0.9968</t>
+  </si>
+  <si>
+    <t>0.0050,0.0039,0.0018,0.9959</t>
+  </si>
+  <si>
+    <t>0.0029,0.8921,0.9422,0.0007</t>
+  </si>
+  <si>
+    <t>0.0056,0.0885,0.9869,0.0017</t>
+  </si>
+  <si>
+    <t>0.0063,0.6511,0.8635,0.0031</t>
+  </si>
+  <si>
+    <t>0.0007,0.7277,0.9939,0.0002</t>
+  </si>
+  <si>
+    <t>0.0024,0.9050,0.9674,0.0006</t>
+  </si>
+  <si>
+    <t>0.0078,0.9544,0.0432,0.0031</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9926,0.0061,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9928,0.0071,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9946,0.0032,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9966,0.0008,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9948,0.0046,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0014,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9971,0.0002,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9972,0.0002,0.0002,0.0025</t>
+  </si>
+  <si>
+    <t>0.0038,0.0050,0.9926,0.0032</t>
+  </si>
+  <si>
+    <t>0.0085,0.0028,0.9921,0.0007</t>
+  </si>
+  <si>
+    <t>0.9775,0.0025,0.0164,0.0016</t>
+  </si>
+  <si>
+    <t>0.0036,0.0009,0.9954,0.0009</t>
+  </si>
+  <si>
+    <t>0.0072,0.9921,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.0022,0.9941,0.0014,0.0012</t>
+  </si>
+  <si>
+    <t>0.0325,0.9689,0.0022,0.0026</t>
+  </si>
+  <si>
+    <t>0.0693,0.9429,0.0061,0.0027</t>
+  </si>
+  <si>
+    <t>0.0078,0.9910,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0040,0.9923,0.0018,0.0014</t>
+  </si>
+  <si>
+    <t>0.6305,0.5559,0.0021,0.0019</t>
+  </si>
+  <si>
+    <t>0.9051,0.0564,0.0084,0.0093</t>
+  </si>
+  <si>
+    <t>0.5362,0.0025,0.6651,0.0020</t>
+  </si>
+  <si>
+    <t>0.8159,0.0454,0.1408,0.0118</t>
+  </si>
+  <si>
+    <t>0.3896,0.0339,0.5085,0.0939</t>
+  </si>
+  <si>
+    <t>0.0403,0.0840,0.0585,0.9319</t>
+  </si>
+  <si>
+    <t>0.0065,0.9855,0.0056,0.0039</t>
+  </si>
+  <si>
+    <t>0.0080,0.9860,0.0089,0.0008</t>
+  </si>
+  <si>
+    <t>0.0019,0.9895,0.0051,0.0122</t>
+  </si>
+  <si>
+    <t>0.0009,0.6426,0.9728,0.0009</t>
+  </si>
+  <si>
+    <t>0.0186,0.9828,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.9077,0.0682,0.0347,0.0022</t>
+  </si>
+  <si>
+    <t>0.6953,0.4248,0.0082,0.0033</t>
+  </si>
+  <si>
+    <t>0.9903,0.0017,0.0012,0.0058</t>
+  </si>
+  <si>
+    <t>0.9965,0.0004,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9944,0.0011,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9914,0.0011,0.0074,0.0005</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9965,0.0004,0.0034,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9937,0.0010,0.0032,0.0015</t>
+  </si>
+  <si>
+    <t>0.0065,0.1035,0.9802,0.0066</t>
+  </si>
+  <si>
+    <t>0.0016,0.2968,0.9887,0.0004</t>
+  </si>
+  <si>
+    <t>0.0094,0.0201,0.9812,0.0023</t>
+  </si>
+  <si>
+    <t>0.2087,0.0048,0.8491,0.0061</t>
+  </si>
+  <si>
+    <t>0.9818,0.0009,0.0146,0.0011</t>
+  </si>
+  <si>
+    <t>0.9404,0.0119,0.0419,0.0072</t>
+  </si>
+  <si>
+    <t>0.4875,0.0182,0.6491,0.0052</t>
+  </si>
+  <si>
+    <t>0.8642,0.0118,0.1749,0.0051</t>
+  </si>
+  <si>
+    <t>0.0735,0.0002,0.0005,0.9820</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0018,0.9993</t>
+  </si>
+  <si>
+    <t>0.0031,0.0090,0.0011,0.9969</t>
+  </si>
+  <si>
+    <t>0.0041,0.0006,0.0005,0.9980</t>
+  </si>
+  <si>
+    <t>0.0012,0.9860,0.3249,0.0015</t>
+  </si>
+  <si>
+    <t>0.9967,0.0004,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.4645,0.6212,0.0035,0.0113</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.2597,0.8384,0.0032,0.0015</t>
+  </si>
+  <si>
+    <t>0.9942,0.0005,0.0009,0.0015</t>
+  </si>
+  <si>
+    <t>0.6887,0.0053,0.0019,0.4301</t>
+  </si>
+  <si>
+    <t>0.9883,0.0006,0.0118,0.0007</t>
+  </si>
+  <si>
+    <t>0.0080,0.0119,0.8904,0.3352</t>
+  </si>
+  <si>
+    <t>0.5714,0.0026,0.0032,0.6419</t>
+  </si>
+  <si>
+    <t>0.9652,0.0004,0.0004,0.0550</t>
+  </si>
+  <si>
+    <t>0.3122,0.4691,0.2081,0.0199</t>
+  </si>
+  <si>
+    <t>0.9926,0.0019,0.0007,0.0016</t>
+  </si>
+  <si>
+    <t>0.9931,0.0013,0.0032,0.0005</t>
+  </si>
+  <si>
+    <t>0.8064,0.1655,0.0315,0.0155</t>
+  </si>
+  <si>
+    <t>0.9652,0.0134,0.0141,0.0011</t>
+  </si>
+  <si>
+    <t>0.9854,0.0056,0.0058,0.0009</t>
+  </si>
+  <si>
+    <t>0.9967,0.0005,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9972,0.0009,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9962,0.0021,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0001,0.0002,0.0025</t>
+  </si>
+  <si>
+    <t>0.9935,0.0020,0.0020,0.0011</t>
+  </si>
+  <si>
+    <t>0.9874,0.0039,0.0038,0.0025</t>
+  </si>
+  <si>
+    <t>0.9971,0.0003,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9893,0.0008,0.0003,0.0083</t>
+  </si>
+  <si>
+    <t>0.8641,0.1409,0.0029,0.0089</t>
+  </si>
+  <si>
+    <t>0.4331,0.7660,0.0023,0.0007</t>
+  </si>
+  <si>
+    <t>0.8068,0.3573,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.0374,0.1553,0.9703,0.0036</t>
+  </si>
+  <si>
+    <t>0.9911,0.0055,0.0008,0.0016</t>
+  </si>
+  <si>
+    <t>0.9702,0.0196,0.0065,0.0012</t>
+  </si>
+  <si>
+    <t>0.9974,0.0006,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9797,0.0265,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0062,0.9994,0.0009</t>
+  </si>
+  <si>
+    <t>0.9627,0.0197,0.0175,0.0015</t>
+  </si>
+  <si>
+    <t>0.0089,0.0018,0.9898,0.0006</t>
+  </si>
+  <si>
+    <t>0.0011,0.3711,0.9966,0.0005</t>
+  </si>
+  <si>
+    <t>0.0019,0.0017,0.9951,0.0025</t>
+  </si>
+  <si>
+    <t>0.0057,0.2564,0.9911,0.0017</t>
+  </si>
+  <si>
+    <t>0.0019,0.0026,0.9958,0.0017</t>
+  </si>
+  <si>
+    <t>0.0040,0.0015,0.9948,0.0006</t>
+  </si>
+  <si>
+    <t>0.0044,0.0073,0.9926,0.0010</t>
+  </si>
+  <si>
+    <t>0.0915,0.0188,0.9004,0.0099</t>
+  </si>
+  <si>
+    <t>0.0479,0.0165,0.9393,0.0122</t>
+  </si>
+  <si>
+    <t>0.1358,0.0071,0.9048,0.0013</t>
+  </si>
+  <si>
+    <t>0.0702,0.0147,0.9294,0.0017</t>
+  </si>
+  <si>
+    <t>0.0338,0.0387,0.9402,0.0018</t>
+  </si>
+  <si>
+    <t>0.4579,0.0760,0.5320,0.0419</t>
+  </si>
+  <si>
+    <t>0.4059,0.0168,0.6724,0.0137</t>
+  </si>
+  <si>
+    <t>0.0406,0.1772,0.8341,0.0065</t>
+  </si>
+  <si>
+    <t>0.3917,0.8207,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.0891,0.9531,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.9297,0.1549,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9952,0.0036,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9891,0.0128,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.7539,0.0406,0.2236,0.0457</t>
+  </si>
+  <si>
+    <t>0.9409,0.0042,0.0406,0.0091</t>
+  </si>
+  <si>
+    <t>0.4209,0.0016,0.0156,0.5907</t>
+  </si>
+  <si>
+    <t>0.6258,0.0022,0.5507,0.0031</t>
+  </si>
+  <si>
+    <t>0.8109,0.0032,0.1180,0.0261</t>
+  </si>
+  <si>
+    <t>0.0030,0.0022,0.9928,0.0029</t>
+  </si>
+  <si>
+    <t>0.0063,0.0477,0.9658,0.0133</t>
+  </si>
+  <si>
+    <t>0.0521,0.0774,0.9449,0.0024</t>
+  </si>
+  <si>
+    <t>0.1235,0.0209,0.8993,0.0057</t>
+  </si>
+  <si>
+    <t>0.0439,0.0164,0.9339,0.0054</t>
+  </si>
+  <si>
+    <t>0.9979,0.0005,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9942,0.0028,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9925,0.0034,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9936,0.0064,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9940,0.0021,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9965,0.0004,0.0002,0.0019</t>
+  </si>
+  <si>
+    <t>0.9970,0.0005,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.0008,0.0131,0.9984,0.0009</t>
+  </si>
+  <si>
+    <t>0.0731,0.7347,0.4111,0.0037</t>
+  </si>
+  <si>
+    <t>0.9717,0.0053,0.0200,0.0031</t>
+  </si>
+  <si>
+    <t>0.0063,0.0011,0.9948,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0034,0.9921,0.0084</t>
+  </si>
+  <si>
+    <t>0.0009,0.0219,0.9968,0.0006</t>
+  </si>
+  <si>
+    <t>0.0038,0.0013,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0049,0.0059,0.9880,0.0037</t>
+  </si>
+  <si>
+    <t>0.0010,0.0039,0.9967,0.0019</t>
+  </si>
+  <si>
+    <t>0.0125,0.0163,0.9734,0.0089</t>
+  </si>
+  <si>
+    <t>0.0348,0.0114,0.9416,0.0140</t>
+  </si>
+  <si>
+    <t>0.8335,0.0031,0.2487,0.0043</t>
+  </si>
+  <si>
+    <t>0.9379,0.0002,0.1292,0.0005</t>
+  </si>
+  <si>
+    <t>0.9716,0.0032,0.0179,0.0037</t>
+  </si>
+  <si>
+    <t>0.9949,0.0046,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9955,0.0033,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9931,0.0044,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9971,0.0002,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.9977,0.0006,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9926,0.0078,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.0057,0.0348,0.9873,0.0005</t>
+  </si>
+  <si>
+    <t>0.0027,0.0142,0.9962,0.0004</t>
+  </si>
+  <si>
+    <t>0.0176,0.0338,0.9590,0.0099</t>
+  </si>
+  <si>
+    <t>0.0136,0.0069,0.9816,0.0010</t>
+  </si>
+  <si>
+    <t>0.0097,0.0012,0.9938,0.0002</t>
+  </si>
+  <si>
+    <t>0.0266,0.0233,0.9315,0.0636</t>
+  </si>
+  <si>
+    <t>0.5439,0.0033,0.6577,0.0017</t>
+  </si>
+  <si>
+    <t>0.1597,0.0012,0.8711,0.0036</t>
+  </si>
+  <si>
+    <t>0.9395,0.0002,0.0007,0.1064</t>
+  </si>
+  <si>
+    <t>0.0289,0.0258,0.0031,0.9819</t>
+  </si>
+  <si>
+    <t>0.1795,0.0015,0.0003,0.9425</t>
+  </si>
+  <si>
+    <t>0.0021,0.0000,0.0002,0.9991</t>
+  </si>
+  <si>
+    <t>0.0021,0.0018,0.0012,0.9982</t>
+  </si>
+  <si>
+    <t>0.9844,0.0025,0.0006,0.0054</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2891,7 +2891,7 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D69" t="s">
         <v>331</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3185,7 +3185,7 @@
         <v>259</v>
       </c>
       <c r="C90" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D90" t="s">
         <v>352</v>
@@ -3283,7 +3283,7 @@
         <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D97" t="s">
         <v>359</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4123,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
         <v>419</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4795,7 +4795,7 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
         <v>467</v>
@@ -4809,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
         <v>468</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
